--- a/data/trans_dic/P21_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,11; 19,23</t>
+          <t>10,63; 19,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,11; 40,46</t>
+          <t>29,06; 39,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,17; 34,62</t>
+          <t>23,11; 33,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,16; 41,32</t>
+          <t>27,94; 41,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,77; 27,06</t>
+          <t>17,04; 27,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,22; 45,92</t>
+          <t>33,15; 44,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,54; 42,32</t>
+          <t>31,14; 42,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,29; 44,19</t>
+          <t>34,73; 44,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,85; 21,39</t>
+          <t>14,56; 21,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,51; 40,77</t>
+          <t>32,71; 40,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,36; 36,44</t>
+          <t>28,4; 36,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,33; 40,88</t>
+          <t>32,5; 40,86</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,18; 19,35</t>
+          <t>12,56; 19,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,07; 29,89</t>
+          <t>22,33; 30,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,52; 20,18</t>
+          <t>13,26; 19,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 20,3</t>
+          <t>11,72; 19,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,31; 29,35</t>
+          <t>21,89; 29,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,72; 42,89</t>
+          <t>34,02; 42,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,63; 25,2</t>
+          <t>17,43; 24,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,23; 23,44</t>
+          <t>17,34; 23,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,93; 23,02</t>
+          <t>17,91; 22,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,19; 35,02</t>
+          <t>29,13; 35,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,19; 21,2</t>
+          <t>16,58; 21,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,09; 20,25</t>
+          <t>14,94; 20,17</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,2; 26,64</t>
+          <t>17,23; 26,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,14; 28,21</t>
+          <t>19,15; 28,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,76; 15,65</t>
+          <t>8,68; 15,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,42; 27,62</t>
+          <t>18,45; 27,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,09; 30,64</t>
+          <t>21,04; 30,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,24; 33,33</t>
+          <t>23,2; 33,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,7; 18,33</t>
+          <t>10,63; 18,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,22; 36,97</t>
+          <t>28,07; 36,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,26; 26,95</t>
+          <t>20,24; 27,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,4; 29,47</t>
+          <t>22,61; 29,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,73; 15,89</t>
+          <t>10,56; 16,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,8; 30,85</t>
+          <t>24,34; 30,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,96; 25,31</t>
+          <t>17,04; 25,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,15; 26,36</t>
+          <t>17,72; 26,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,18; 31,35</t>
+          <t>21,7; 31,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,01; 31,07</t>
+          <t>18,92; 30,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,49; 32,72</t>
+          <t>23,66; 32,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,73; 32,19</t>
+          <t>22,65; 32,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,38; 37,32</t>
+          <t>27,13; 37,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,71; 25,17</t>
+          <t>11,7; 25,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,54; 27,51</t>
+          <t>21,57; 27,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,09; 27,37</t>
+          <t>20,87; 27,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,9; 33,03</t>
+          <t>26,1; 33,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,53; 26,08</t>
+          <t>15,18; 25,65</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,34; 22,56</t>
+          <t>12,21; 23,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,55; 22,81</t>
+          <t>12,78; 23,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 18,27</t>
+          <t>8,21; 17,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,09; 14,19</t>
+          <t>6,17; 15,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,79; 26,13</t>
+          <t>15,0; 26,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,03; 43,26</t>
+          <t>29,17; 42,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,6; 18,58</t>
+          <t>9,97; 19,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,08</t>
+          <t>3,17; 7,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,08; 22,61</t>
+          <t>14,91; 22,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,55; 31,32</t>
+          <t>22,76; 31,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,42; 16,76</t>
+          <t>10,28; 16,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,44</t>
+          <t>5,17; 9,48</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,98; 26,89</t>
+          <t>16,83; 26,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,77; 28,89</t>
+          <t>18,3; 28,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,46; 27,62</t>
+          <t>16,76; 27,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20,86; 30,39</t>
+          <t>21,15; 30,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,28; 37,2</t>
+          <t>25,99; 37,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,5; 39,7</t>
+          <t>29,09; 40,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,87; 33,64</t>
+          <t>22,78; 33,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,87; 34,1</t>
+          <t>24,99; 34,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,72; 30,6</t>
+          <t>23,15; 30,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,46; 32,99</t>
+          <t>25,26; 33,27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,25; 28,79</t>
+          <t>21,33; 28,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,16; 30,95</t>
+          <t>24,18; 30,59</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,85; 21,14</t>
+          <t>15,06; 21,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,06; 25,58</t>
+          <t>18,62; 25,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,96; 14,17</t>
+          <t>8,98; 14,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,5; 31,46</t>
+          <t>23,06; 31,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,11; 30,14</t>
+          <t>23,1; 29,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,53; 30,82</t>
+          <t>23,89; 30,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,2; 21,33</t>
+          <t>15,06; 21,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,97; 79,85</t>
+          <t>33,77; 75,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,03; 24,7</t>
+          <t>20,21; 24,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22,37; 27,23</t>
+          <t>22,25; 26,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,93; 16,92</t>
+          <t>12,96; 16,92</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,0; 63,07</t>
+          <t>30,11; 65,99</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,89; 16,08</t>
+          <t>10,58; 15,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,89; 11,47</t>
+          <t>6,84; 11,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,17; 16,08</t>
+          <t>10,91; 15,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,72; 13,96</t>
+          <t>4,08; 14,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,42; 22,44</t>
+          <t>16,37; 22,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,53; 15,58</t>
+          <t>10,45; 15,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,79; 20,05</t>
+          <t>14,71; 20,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,34; 18,05</t>
+          <t>13,33; 17,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,82; 18,53</t>
+          <t>14,69; 18,44</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,48; 12,74</t>
+          <t>9,48; 12,77</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13,49; 17,16</t>
+          <t>13,62; 17,28</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,4; 15,05</t>
+          <t>7,62; 15,03</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,91; 18,54</t>
+          <t>15,73; 18,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19,24; 22,17</t>
+          <t>19,3; 22,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,33; 17,98</t>
+          <t>15,4; 17,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15,24; 21,67</t>
+          <t>15,17; 21,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,94; 25,86</t>
+          <t>22,94; 25,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,08; 29,2</t>
+          <t>26,13; 29,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,07; 22,89</t>
+          <t>20,19; 23,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23,87; 43,22</t>
+          <t>23,92; 42,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,81; 21,78</t>
+          <t>19,83; 21,8</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23,15; 25,26</t>
+          <t>23,13; 25,28</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,17; 20,13</t>
+          <t>18,16; 20,11</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,15; 32,19</t>
+          <t>21,47; 32,67</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30343; 52488</t>
+          <t>29015; 52134</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85587; 118959</t>
+          <t>85434; 117241</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68060; 101700</t>
+          <t>67901; 98858</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87706; 128697</t>
+          <t>87017; 129162</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>43743; 70592</t>
+          <t>44437; 71159</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95045; 131373</t>
+          <t>94836; 127492</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90497; 121401</t>
+          <t>89348; 122416</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>99314; 127984</t>
+          <t>100597; 127867</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79285; 114182</t>
+          <t>77731; 112387</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>188586; 236478</t>
+          <t>189730; 237171</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>164666; 211590</t>
+          <t>164902; 210528</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>194356; 245698</t>
+          <t>195332; 245614</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60064; 95428</t>
+          <t>61937; 94979</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>111554; 151110</t>
+          <t>112870; 152229</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67929; 101404</t>
+          <t>66654; 100186</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61267; 105220</t>
+          <t>60755; 102342</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>107387; 147912</t>
+          <t>110331; 147318</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>176635; 224646</t>
+          <t>178194; 224409</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92219; 131811</t>
+          <t>91158; 130162</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>88594; 120496</t>
+          <t>89148; 120020</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178765; 229501</t>
+          <t>178556; 228189</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>300417; 360434</t>
+          <t>299833; 361787</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>166038; 217394</t>
+          <t>170092; 222526</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>155793; 209107</t>
+          <t>154206; 208240</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>54828; 84954</t>
+          <t>54943; 84804</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62018; 91414</t>
+          <t>62055; 90965</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27432; 49015</t>
+          <t>27178; 48970</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58202; 87309</t>
+          <t>58316; 88042</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>70724; 102754</t>
+          <t>70582; 102957</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79261; 113665</t>
+          <t>79114; 115337</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35712; 61193</t>
+          <t>35485; 62221</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>98368; 128865</t>
+          <t>97860; 128178</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>132553; 176313</t>
+          <t>132411; 176963</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148952; 196020</t>
+          <t>150383; 194944</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69388; 102782</t>
+          <t>68297; 103554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>164804; 205033</t>
+          <t>161778; 204469</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60831; 90782</t>
+          <t>61117; 91043</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64137; 98584</t>
+          <t>66287; 98758</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81417; 115068</t>
+          <t>79629; 114692</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59091; 96570</t>
+          <t>58797; 95552</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87258; 121544</t>
+          <t>87877; 121760</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88194; 124892</t>
+          <t>87867; 124613</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>106045; 144527</t>
+          <t>105087; 145436</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55717; 119741</t>
+          <t>55642; 120193</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>157301; 200884</t>
+          <t>157512; 204144</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>160736; 208545</t>
+          <t>159034; 210083</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>195391; 249127</t>
+          <t>196852; 253490</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>122141; 205150</t>
+          <t>119382; 201748</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25086; 45868</t>
+          <t>24819; 46757</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26678; 48509</t>
+          <t>27174; 48983</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18467; 38173</t>
+          <t>17153; 35926</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10883; 25361</t>
+          <t>11029; 27543</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30714; 54265</t>
+          <t>31143; 54306</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>65942; 94987</t>
+          <t>64058; 93409</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20893; 40455</t>
+          <t>21710; 42362</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6685; 14779</t>
+          <t>6619; 14876</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61976; 92937</t>
+          <t>61283; 92711</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>97447; 135348</t>
+          <t>98362; 135608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44462; 71509</t>
+          <t>43847; 72134</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20028; 36573</t>
+          <t>20020; 36726</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>45977; 72811</t>
+          <t>45580; 73017</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51437; 79160</t>
+          <t>50126; 78077</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45937; 72668</t>
+          <t>44098; 71761</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56252; 81932</t>
+          <t>57030; 81896</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>72847; 103121</t>
+          <t>72047; 103605</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>79805; 111185</t>
+          <t>81449; 112346</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62468; 91868</t>
+          <t>62222; 91612</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>63926; 87667</t>
+          <t>64236; 87937</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>124496; 167675</t>
+          <t>126865; 164989</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>141078; 182789</t>
+          <t>139951; 184316</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113944; 154386</t>
+          <t>114371; 154836</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>127261; 163022</t>
+          <t>127347; 161106</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>91223; 129851</t>
+          <t>92471; 131259</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>126305; 169513</t>
+          <t>123442; 168405</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58801; 93004</t>
+          <t>58950; 95901</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>140486; 196396</t>
+          <t>143965; 196429</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>147478; 192328</t>
+          <t>147399; 191101</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>163251; 213863</t>
+          <t>165772; 213664</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>104889; 147153</t>
+          <t>103892; 146872</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>287110; 674783</t>
+          <t>285380; 640378</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>250815; 309384</t>
+          <t>253115; 309325</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>303465; 369391</t>
+          <t>301902; 363583</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>174055; 227787</t>
+          <t>174551; 227796</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>440866; 926737</t>
+          <t>442388; 969565</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>81025; 119565</t>
+          <t>78694; 118565</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>53572; 89123</t>
+          <t>53169; 88231</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>86945; 125223</t>
+          <t>84960; 123530</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>34516; 129638</t>
+          <t>37924; 131409</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>128670; 175800</t>
+          <t>128270; 175700</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>86683; 128222</t>
+          <t>85963; 126101</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>122208; 165656</t>
+          <t>121505; 165970</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>95392; 128999</t>
+          <t>95312; 128343</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>226334; 283042</t>
+          <t>224289; 281586</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>151726; 203789</t>
+          <t>151661; 204335</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>216413; 275413</t>
+          <t>218561; 277371</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>121667; 247353</t>
+          <t>125273; 246991</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>521268; 607385</t>
+          <t>515224; 602739</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>658662; 759263</t>
+          <t>660984; 758293</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>518647; 608351</t>
+          <t>521233; 605503</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>527034; 749197</t>
+          <t>524524; 755954</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>774989; 873724</t>
+          <t>774864; 872861</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>927222; 1038189</t>
+          <t>928969; 1042891</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>710011; 809947</t>
+          <t>714275; 817333</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>871974; 1578998</t>
+          <t>873901; 1535499</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1317955; 1449133</t>
+          <t>1319432; 1450792</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1615706; 1763105</t>
+          <t>1614116; 1764599</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1257784; 1393367</t>
+          <t>1256781; 1391939</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1504178; 2288957</t>
+          <t>1526592; 2323565</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,63; 19,1</t>
+          <t>10,65; 18,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,06; 39,88</t>
+          <t>28,37; 39,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,11; 33,65</t>
+          <t>23,44; 34,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,94; 41,47</t>
+          <t>27,93; 38,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,04; 27,28</t>
+          <t>16,45; 26,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,15; 44,57</t>
+          <t>33,0; 45,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,14; 42,67</t>
+          <t>30,67; 42,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,73; 44,15</t>
+          <t>34,26; 43,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,56; 21,05</t>
+          <t>14,25; 21,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,71; 40,89</t>
+          <t>32,67; 40,92</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,4; 36,26</t>
+          <t>28,46; 36,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,5; 40,86</t>
+          <t>32,31; 39,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,56; 19,26</t>
+          <t>12,14; 19,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,33; 30,11</t>
+          <t>22,18; 30,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,26; 19,93</t>
+          <t>13,25; 20,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 19,74</t>
+          <t>11,66; 19,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,89; 29,23</t>
+          <t>21,86; 29,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,02; 42,85</t>
+          <t>34,15; 42,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,43; 24,88</t>
+          <t>17,27; 24,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,34; 23,35</t>
+          <t>16,85; 22,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,91; 22,89</t>
+          <t>18,01; 23,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,13; 35,15</t>
+          <t>29,09; 34,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,58; 21,7</t>
+          <t>16,52; 21,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,94; 20,17</t>
+          <t>15,05; 20,0</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,23; 26,6</t>
+          <t>17,1; 26,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,15; 28,07</t>
+          <t>18,9; 28,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,68; 15,64</t>
+          <t>8,88; 15,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,45; 27,86</t>
+          <t>19,52; 28,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,04; 30,7</t>
+          <t>21,28; 30,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,2; 33,82</t>
+          <t>23,52; 33,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,63; 18,64</t>
+          <t>10,79; 18,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,07; 36,77</t>
+          <t>28,1; 36,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,24; 27,05</t>
+          <t>20,37; 27,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,61; 29,31</t>
+          <t>22,59; 29,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,56; 16,01</t>
+          <t>10,39; 15,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,34; 30,76</t>
+          <t>25,38; 31,7</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,04; 25,38</t>
+          <t>16,68; 25,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,72; 26,41</t>
+          <t>17,59; 26,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,7; 31,25</t>
+          <t>21,75; 31,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,92; 30,74</t>
+          <t>19,37; 31,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,66; 32,78</t>
+          <t>23,7; 32,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,65; 32,12</t>
+          <t>22,6; 31,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,13; 37,55</t>
+          <t>27,43; 37,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,7; 25,27</t>
+          <t>21,14; 29,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,57; 27,96</t>
+          <t>21,47; 27,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,87; 27,57</t>
+          <t>20,97; 27,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,1; 33,61</t>
+          <t>26,04; 33,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,18; 25,65</t>
+          <t>21,41; 28,82</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,21; 23,0</t>
+          <t>11,97; 22,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,78; 23,04</t>
+          <t>12,31; 22,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,21; 17,19</t>
+          <t>8,21; 17,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 15,41</t>
+          <t>5,43; 13,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,0; 26,15</t>
+          <t>14,68; 26,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,17; 42,54</t>
+          <t>29,61; 42,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,97; 19,46</t>
+          <t>9,94; 18,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,13</t>
+          <t>3,13; 6,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,91; 22,56</t>
+          <t>15,02; 22,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,76; 31,38</t>
+          <t>22,86; 31,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,28; 16,91</t>
+          <t>10,07; 16,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,48</t>
+          <t>5,14; 9,1</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,83; 26,96</t>
+          <t>16,83; 27,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,3; 28,5</t>
+          <t>19,05; 29,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,76; 27,27</t>
+          <t>17,38; 27,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,15; 30,37</t>
+          <t>21,0; 30,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,99; 37,38</t>
+          <t>26,03; 37,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,09; 40,12</t>
+          <t>28,88; 40,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,78; 33,54</t>
+          <t>22,24; 33,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,99; 34,21</t>
+          <t>24,69; 33,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,15; 30,11</t>
+          <t>22,79; 30,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,26; 33,27</t>
+          <t>25,17; 32,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,33; 28,87</t>
+          <t>21,77; 29,5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,18; 30,59</t>
+          <t>24,05; 30,62</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,06; 21,37</t>
+          <t>14,9; 21,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,62; 25,41</t>
+          <t>18,9; 25,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,98; 14,61</t>
+          <t>8,95; 14,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,06; 31,46</t>
+          <t>22,95; 30,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,1; 29,94</t>
+          <t>22,91; 29,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,89; 30,79</t>
+          <t>23,47; 30,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,06; 21,29</t>
+          <t>15,48; 21,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,77; 75,78</t>
+          <t>31,5; 37,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,21; 24,7</t>
+          <t>20,0; 24,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22,25; 26,8</t>
+          <t>22,19; 27,28</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,96; 16,92</t>
+          <t>12,95; 16,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,11; 65,99</t>
+          <t>28,31; 33,31</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,58; 15,94</t>
+          <t>10,88; 16,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,84; 11,35</t>
+          <t>6,86; 11,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,91; 15,87</t>
+          <t>10,91; 15,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 14,15</t>
+          <t>10,73; 15,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,37; 22,42</t>
+          <t>16,47; 22,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,45; 15,32</t>
+          <t>10,59; 15,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,71; 20,09</t>
+          <t>14,73; 19,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,33; 17,95</t>
+          <t>13,27; 17,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,69; 18,44</t>
+          <t>14,53; 18,2</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,48; 12,77</t>
+          <t>9,39; 12,79</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13,62; 17,28</t>
+          <t>13,52; 17,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,62; 15,03</t>
+          <t>12,57; 15,98</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,73; 18,4</t>
+          <t>15,89; 18,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19,3; 22,15</t>
+          <t>19,09; 22,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,4; 17,89</t>
+          <t>15,53; 18,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15,17; 21,86</t>
+          <t>19,27; 22,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,94; 25,84</t>
+          <t>22,88; 25,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,13; 29,33</t>
+          <t>26,2; 29,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,19; 23,1</t>
+          <t>20,17; 23,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23,92; 42,03</t>
+          <t>23,84; 26,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,83; 21,8</t>
+          <t>19,78; 21,85</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23,13; 25,28</t>
+          <t>23,18; 25,29</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,16; 20,11</t>
+          <t>18,27; 20,22</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,47; 32,67</t>
+          <t>22,02; 24,01</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106964</t>
+          <t>106088</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>113473</t>
+          <t>121762</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>220436</t>
+          <t>227850</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29015; 52134</t>
+          <t>29074; 51003</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85434; 117241</t>
+          <t>83412; 116531</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67901; 98858</t>
+          <t>68850; 101621</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87017; 129162</t>
+          <t>89049; 123769</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44437; 71159</t>
+          <t>42918; 70018</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94836; 127492</t>
+          <t>94411; 129952</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89348; 122416</t>
+          <t>87979; 121951</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100597; 127867</t>
+          <t>108283; 137246</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77731; 112387</t>
+          <t>76094; 113883</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>189730; 237171</t>
+          <t>189521; 237375</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>164902; 210528</t>
+          <t>165239; 210686</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>195332; 245614</t>
+          <t>205124; 250109</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78622</t>
+          <t>80932</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>103078</t>
+          <t>108245</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>181700</t>
+          <t>189177</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61937; 94979</t>
+          <t>59880; 94596</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>112870; 152229</t>
+          <t>112107; 153553</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66654; 100186</t>
+          <t>66608; 101225</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60755; 102342</t>
+          <t>61888; 102527</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>110331; 147318</t>
+          <t>110157; 147939</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>178194; 224409</t>
+          <t>178855; 223082</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91158; 130162</t>
+          <t>90327; 129212</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89148; 120020</t>
+          <t>91936; 125064</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178556; 228189</t>
+          <t>179588; 229893</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>299833; 361787</t>
+          <t>299374; 359768</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>170092; 222526</t>
+          <t>169440; 219068</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>154206; 208240</t>
+          <t>161973; 215235</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71809</t>
+          <t>74776</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>112167</t>
+          <t>114616</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>183976</t>
+          <t>189392</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>54943; 84804</t>
+          <t>54531; 84720</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62055; 90965</t>
+          <t>61232; 91547</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27178; 48970</t>
+          <t>27818; 49624</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58316; 88042</t>
+          <t>61692; 91471</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>70582; 102957</t>
+          <t>71388; 103745</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79114; 115337</t>
+          <t>80218; 114947</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35485; 62221</t>
+          <t>36010; 61555</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>97860; 128178</t>
+          <t>99973; 129788</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>132411; 176963</t>
+          <t>133275; 177650</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>150383; 194944</t>
+          <t>150251; 196715</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68297; 103554</t>
+          <t>67202; 101741</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>161778; 204469</t>
+          <t>170534; 213002</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76327</t>
+          <t>90105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>92154</t>
+          <t>106735</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>168481</t>
+          <t>196840</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61117; 91043</t>
+          <t>59837; 90674</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66287; 98758</t>
+          <t>65795; 98548</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79629; 114692</t>
+          <t>79840; 116914</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58797; 95552</t>
+          <t>71900; 117738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87877; 121760</t>
+          <t>88027; 119612</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87867; 124613</t>
+          <t>87675; 123228</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>105087; 145436</t>
+          <t>106215; 145700</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55642; 120193</t>
+          <t>89188; 126279</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>157512; 204144</t>
+          <t>156760; 200080</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>159034; 210083</t>
+          <t>159815; 210031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>196852; 253490</t>
+          <t>196396; 249655</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>119382; 201748</t>
+          <t>169830; 228584</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17208</t>
+          <t>18799</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27300</t>
+          <t>29803</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24819; 46757</t>
+          <t>24331; 45999</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27174; 48983</t>
+          <t>26167; 48371</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17153; 35926</t>
+          <t>17164; 36040</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11029; 27543</t>
+          <t>11167; 28419</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>31143; 54306</t>
+          <t>30477; 55954</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>64058; 93409</t>
+          <t>65022; 93684</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21710; 42362</t>
+          <t>21652; 40578</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6619; 14876</t>
+          <t>7121; 15531</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61283; 92711</t>
+          <t>61715; 93198</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>98362; 135608</t>
+          <t>98821; 134333</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43847; 72134</t>
+          <t>42948; 71326</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20020; 36726</t>
+          <t>22268; 39404</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>68278</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>75774</t>
+          <t>77225</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>144560</t>
+          <t>145504</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>45580; 73017</t>
+          <t>45590; 74457</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>50126; 78077</t>
+          <t>52201; 80196</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44098; 71761</t>
+          <t>45721; 71910</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57030; 81896</t>
+          <t>56856; 81908</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>72047; 103605</t>
+          <t>72146; 102838</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>81449; 112346</t>
+          <t>80881; 112897</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62222; 91612</t>
+          <t>60730; 91646</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>64236; 87937</t>
+          <t>65111; 89543</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>126865; 164989</t>
+          <t>124890; 167038</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>139951; 184316</t>
+          <t>139421; 181763</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>114371; 154836</t>
+          <t>116756; 158216</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>127347; 161106</t>
+          <t>128521; 163662</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167436</t>
+          <t>192031</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>428512</t>
+          <t>266194</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>595948</t>
+          <t>458224</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>92471; 131259</t>
+          <t>91510; 132548</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>123442; 168405</t>
+          <t>125271; 171857</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58950; 95901</t>
+          <t>58745; 93567</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>143965; 196429</t>
+          <t>165159; 220058</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>147399; 191101</t>
+          <t>146201; 190097</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>165772; 213664</t>
+          <t>162862; 213158</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>103892; 146872</t>
+          <t>106838; 148121</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>285380; 640378</t>
+          <t>241859; 291176</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>253115; 309325</t>
+          <t>250450; 309136</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>301902; 363583</t>
+          <t>301074; 370075</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>174551; 227796</t>
+          <t>174321; 226190</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>442388; 969565</t>
+          <t>421060; 495403</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>89772</t>
+          <t>102172</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>111238</t>
+          <t>128949</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>201010</t>
+          <t>231122</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>78694; 118565</t>
+          <t>80892; 119903</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>53169; 88231</t>
+          <t>53329; 88196</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>84960; 123530</t>
+          <t>84906; 124406</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>37924; 131409</t>
+          <t>85595; 123987</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>128270; 175700</t>
+          <t>129044; 175100</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>85963; 126101</t>
+          <t>87155; 128125</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>121505; 165970</t>
+          <t>121655; 165019</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>95312; 128343</t>
+          <t>110157; 148123</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>224289; 281586</t>
+          <t>221895; 277911</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>151661; 204335</t>
+          <t>150198; 204640</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>218561; 277371</t>
+          <t>216893; 274556</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>125273; 246991</t>
+          <t>204716; 260139</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>676924</t>
+          <t>733182</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1046486</t>
+          <t>934729</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1723411</t>
+          <t>1667911</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>515224; 602739</t>
+          <t>520496; 605763</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>660984; 758293</t>
+          <t>653775; 753657</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>521233; 605503</t>
+          <t>525366; 610908</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>524524; 755954</t>
+          <t>680550; 786603</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>774864; 872861</t>
+          <t>772794; 869588</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>928969; 1042891</t>
+          <t>931378; 1040224</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>714275; 817333</t>
+          <t>713789; 813841</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>873901; 1535499</t>
+          <t>888878; 978948</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1319432; 1450792</t>
+          <t>1316431; 1454107</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1614116; 1764599</t>
+          <t>1617893; 1765029</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1256781; 1391939</t>
+          <t>1264567; 1399609</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1526592; 2323565</t>
+          <t>1598604; 1743154</t>
         </is>
       </c>
     </row>
